--- a/data/live/environmental/latest_snapshot.xlsx
+++ b/data/live/environmental/latest_snapshot.xlsx
@@ -491,10 +491,10 @@
         <v>91.17</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F2" t="n">
-        <v>27.9</v>
+        <v>27.3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -512,7 +512,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:33</t>
+          <t>2026-08-21 13:35</t>
         </is>
       </c>
     </row>
@@ -534,13 +534,13 @@
         <v>91</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F3" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0.351</v>
@@ -555,7 +555,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:35</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
         <v>26.8</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H4" t="n">
         <v>0.318</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:35</t>
         </is>
       </c>
     </row>
@@ -620,10 +620,10 @@
         <v>90.56</v>
       </c>
       <c r="E5" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F5" t="n">
-        <v>27.4</v>
+        <v>27.1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -641,7 +641,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:35</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
         <v>92.8</v>
       </c>
       <c r="E6" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F6" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="H6" t="n">
         <v>0.457</v>
@@ -684,7 +684,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:35</t>
         </is>
       </c>
     </row>
@@ -706,13 +706,13 @@
         <v>94.8</v>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F7" t="n">
-        <v>26.2</v>
+        <v>25.6</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="H7" t="n">
         <v>0.391</v>
@@ -727,7 +727,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -749,10 +749,10 @@
         <v>90.47</v>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F8" t="n">
-        <v>27.8</v>
+        <v>27.2</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -792,10 +792,10 @@
         <v>92</v>
       </c>
       <c r="E9" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F9" t="n">
-        <v>28.7</v>
+        <v>28.1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -835,13 +835,13 @@
         <v>94.56</v>
       </c>
       <c r="E10" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F10" t="n">
-        <v>27.2</v>
+        <v>26.4</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H10" t="n">
         <v>0.316</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -878,10 +878,10 @@
         <v>89.98</v>
       </c>
       <c r="E11" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>28.3</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -890,16 +890,16 @@
         <v>0.365</v>
       </c>
       <c r="I11" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MODERATE</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -924,10 +924,10 @@
         <v>99</v>
       </c>
       <c r="F12" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="H12" t="n">
         <v>0.379</v>
@@ -942,7 +942,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -964,10 +964,10 @@
         <v>93.03</v>
       </c>
       <c r="E13" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F13" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="G13" t="n">
         <v>0.2</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1007,13 +1007,13 @@
         <v>90.63</v>
       </c>
       <c r="E14" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F14" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0.344</v>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1050,13 +1050,13 @@
         <v>93.97</v>
       </c>
       <c r="E15" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F15" t="n">
-        <v>25.9</v>
+        <v>26.4</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0.324</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1093,13 +1093,13 @@
         <v>92.56999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F16" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="H16" t="n">
         <v>0.391</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
         <v>92.84999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F17" t="n">
         <v>26.9</v>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1179,13 +1179,13 @@
         <v>94.22</v>
       </c>
       <c r="E18" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F18" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="H18" t="n">
         <v>0.3</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1222,13 +1222,13 @@
         <v>91.75</v>
       </c>
       <c r="E19" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F19" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H19" t="n">
         <v>0.35</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1265,13 +1265,13 @@
         <v>91.73999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F20" t="n">
-        <v>26.8</v>
+        <v>26.1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H20" t="n">
         <v>0.355</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1308,13 +1308,13 @@
         <v>93.5</v>
       </c>
       <c r="E21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>22.1</v>
+        <v>21.2</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H21" t="n">
         <v>0.308</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1354,10 +1354,10 @@
         <v>99</v>
       </c>
       <c r="F22" t="n">
-        <v>25.6</v>
+        <v>25.3</v>
       </c>
       <c r="G22" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="H22" t="n">
         <v>0.477</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1394,13 +1394,13 @@
         <v>90.27</v>
       </c>
       <c r="E23" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F23" t="n">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H23" t="n">
         <v>0.341</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1437,13 +1437,13 @@
         <v>94.09999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F24" t="n">
-        <v>26.2</v>
+        <v>27</v>
       </c>
       <c r="G24" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H24" t="n">
         <v>0.36</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1483,10 +1483,10 @@
         <v>97</v>
       </c>
       <c r="F25" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="G25" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="H25" t="n">
         <v>0.345</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1523,13 +1523,13 @@
         <v>92.33</v>
       </c>
       <c r="E26" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F26" t="n">
-        <v>26.7</v>
+        <v>26.9</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="H26" t="n">
         <v>0.348</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-21 10:34</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1566,13 +1566,13 @@
         <v>92.68000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F27" t="n">
-        <v>26.9</v>
+        <v>26.4</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="H27" t="n">
         <v>0.371</v>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-21 10:35</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1609,10 +1609,10 @@
         <v>91.44</v>
       </c>
       <c r="E28" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F28" t="n">
-        <v>28.1</v>
+        <v>27.4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1621,16 +1621,16 @@
         <v>0.36</v>
       </c>
       <c r="I28" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MODERATE</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-21 10:35</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1655,10 +1655,10 @@
         <v>99</v>
       </c>
       <c r="F29" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="G29" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="H29" t="n">
         <v>0.347</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-21 10:35</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1695,13 +1695,13 @@
         <v>92.8</v>
       </c>
       <c r="E30" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F30" t="n">
-        <v>27.3</v>
+        <v>26.9</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="H30" t="n">
         <v>0.341</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-21 10:35</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1738,10 +1738,10 @@
         <v>89.87</v>
       </c>
       <c r="E31" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F31" t="n">
-        <v>27</v>
+        <v>26.7</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1750,7 +1750,7 @@
         <v>0.342</v>
       </c>
       <c r="I31" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-21 10:35</t>
+          <t>2026-08-21 13:36</t>
         </is>
       </c>
     </row>
@@ -1784,10 +1784,10 @@
         <v>99</v>
       </c>
       <c r="F32" t="n">
-        <v>26</v>
+        <v>25.7</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="H32" t="n">
         <v>0.356</v>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-21 10:35</t>
+          <t>2026-08-21 13:37</t>
         </is>
       </c>
     </row>
@@ -1827,10 +1827,10 @@
         <v>93</v>
       </c>
       <c r="F33" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0.339</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-21 10:35</t>
+          <t>2026-08-21 13:37</t>
         </is>
       </c>
     </row>
@@ -1867,13 +1867,13 @@
         <v>92.76000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F34" t="n">
-        <v>27.1</v>
+        <v>26.5</v>
       </c>
       <c r="G34" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="H34" t="n">
         <v>0.348</v>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-21 10:35</t>
+          <t>2026-08-21 13:37</t>
         </is>
       </c>
     </row>
@@ -1910,10 +1910,10 @@
         <v>91.22</v>
       </c>
       <c r="E35" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F35" t="n">
-        <v>28</v>
+        <v>27.3</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-21 10:35</t>
+          <t>2026-08-21 13:37</t>
         </is>
       </c>
     </row>
@@ -1953,10 +1953,10 @@
         <v>91.3</v>
       </c>
       <c r="E36" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F36" t="n">
-        <v>28</v>
+        <v>27.3</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-21 10:35</t>
+          <t>2026-08-21 13:37</t>
         </is>
       </c>
     </row>
